--- a/Convert_from_xlsx_to_Json/table_normalization/employment-table17.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/employment-table17.xlsx
@@ -218,19 +218,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -541,15 +542,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
@@ -557,20 +558,20 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="4">
         <v>2023</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
+      <c r="A5" s="3"/>
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
@@ -587,15 +588,15 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="62" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6"/>
+      <c r="A6" s="3"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="6"/>
@@ -2825,50 +2826,50 @@
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="4"/>
-      <c r="G110" s="4"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="2"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="4"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="2"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A112:G112"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="A111:G111"/>
+    <mergeCell ref="A4:A6"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A110:G110"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A112:G112"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="A111:G111"/>
-    <mergeCell ref="A4:A6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
